--- a/Assets/Resources/DataFiles/CharData/ClassData/1. ExcelFile/StatDataLabel.xlsx
+++ b/Assets/Resources/DataFiles/CharData/ClassData/1. ExcelFile/StatDataLabel.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -639,6 +639,30 @@
       <c r="B17" t="inlineStr">
         <is>
           <t>전기 속성 피해 보너스</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>normalDamage</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>일반공격 피해 증가</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>skillDamage</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>스킬 피해 증가</t>
         </is>
       </c>
     </row>
@@ -653,7 +677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -861,6 +885,30 @@
       <c r="B17" t="inlineStr">
         <is>
           <t>Electric Element Bonus</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>normalDamage</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Normal Attack Damage</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>skillDamage</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Skill Damage</t>
         </is>
       </c>
     </row>
@@ -875,7 +923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1083,6 +1131,30 @@
       <c r="B17" s="3" t="inlineStr">
         <is>
           <t>電気属性ダメージボーナス</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>normalDamage</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>通常攻撃ダメージ増加</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>skillDamage</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>スキルダメージ増加</t>
         </is>
       </c>
     </row>
@@ -1097,7 +1169,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1308,6 +1380,30 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>normalDamage</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>普通攻击伤害提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>skillDamage</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>技能伤害提升</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
